--- a/results_cnn_evaluation(stress_test)/cnn_evaluation(stress_test)_pcc_origin.xlsx
+++ b/results_cnn_evaluation(stress_test)/cnn_evaluation(stress_test)_pcc_origin.xlsx
@@ -8,6 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="nrr_1.0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="nrr_0.75" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="nrr_0.5" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="nrr_0.3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="nrr_0.2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="nrr_0.1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="nrr_0.05" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1066,4 +1072,3898 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>65.06378802747793</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.258199155796319</v>
+      </c>
+      <c r="D2" t="n">
+        <v>65.06378802747793</v>
+      </c>
+      <c r="E2" t="n">
+        <v>62.13629091390609</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>44.35721295387635</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.253651898354292</v>
+      </c>
+      <c r="D3" t="n">
+        <v>44.35721295387635</v>
+      </c>
+      <c r="E3" t="n">
+        <v>39.93087504305447</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>79.78410206084396</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5290292836725712</v>
+      </c>
+      <c r="D4" t="n">
+        <v>79.78410206084396</v>
+      </c>
+      <c r="E4" t="n">
+        <v>79.53262199436146</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>51.22669283611383</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.5157485678792</v>
+      </c>
+      <c r="D5" t="n">
+        <v>51.22669283611384</v>
+      </c>
+      <c r="E5" t="n">
+        <v>50.93560087373289</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>65.16192345436703</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9910236662253737</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65.16192345436703</v>
+      </c>
+      <c r="E6" t="n">
+        <v>63.38575526151826</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>48.77330716388617</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.748066410422325</v>
+      </c>
+      <c r="D7" t="n">
+        <v>48.77330716388617</v>
+      </c>
+      <c r="E7" t="n">
+        <v>48.65380529211635</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>61.53091265947007</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.111899210227421</v>
+      </c>
+      <c r="D8" t="n">
+        <v>61.53091265947007</v>
+      </c>
+      <c r="E8" t="n">
+        <v>60.25449726209894</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>69.97055937193326</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8224107486312278</v>
+      </c>
+      <c r="D9" t="n">
+        <v>69.97055937193328</v>
+      </c>
+      <c r="E9" t="n">
+        <v>68.58166471890198</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>83.80765456329735</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.4053465502802283</v>
+      </c>
+      <c r="D10" t="n">
+        <v>83.80765456329735</v>
+      </c>
+      <c r="E10" t="n">
+        <v>83.88327400090954</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>76.0549558390579</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.6735659949481487</v>
+      </c>
+      <c r="D11" t="n">
+        <v>76.0549558390579</v>
+      </c>
+      <c r="E11" t="n">
+        <v>76.0955339407015</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>74.28851815505398</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.8101412185933441</v>
+      </c>
+      <c r="D12" t="n">
+        <v>74.28851815505398</v>
+      </c>
+      <c r="E12" t="n">
+        <v>73.54123306048328</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>62.61040235525024</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.195983303710818</v>
+      </c>
+      <c r="D13" t="n">
+        <v>62.61040235525025</v>
+      </c>
+      <c r="E13" t="n">
+        <v>61.96875024125017</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>54.17075564278704</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.297749884426594</v>
+      </c>
+      <c r="D14" t="n">
+        <v>54.17075564278705</v>
+      </c>
+      <c r="E14" t="n">
+        <v>52.23081395974764</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>58.58684985279686</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.39483579993248</v>
+      </c>
+      <c r="D15" t="n">
+        <v>58.58684985279686</v>
+      </c>
+      <c r="E15" t="n">
+        <v>52.73050172223247</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>50.44160942100098</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.00198583304882</v>
+      </c>
+      <c r="D16" t="n">
+        <v>50.44160942100098</v>
+      </c>
+      <c r="E16" t="n">
+        <v>39.74537963720547</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>73.50343473994111</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6833494738675654</v>
+      </c>
+      <c r="D17" t="n">
+        <v>73.50343473994113</v>
+      </c>
+      <c r="E17" t="n">
+        <v>73.71239091412048</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>64.18056918547596</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.250926714390516</v>
+      </c>
+      <c r="D18" t="n">
+        <v>64.18056918547596</v>
+      </c>
+      <c r="E18" t="n">
+        <v>63.58501689535607</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>85.37782139352306</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4464769463520497</v>
+      </c>
+      <c r="D19" t="n">
+        <v>85.37782139352305</v>
+      </c>
+      <c r="E19" t="n">
+        <v>85.24741513460793</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>66.73209028459274</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.127404674887657</v>
+      </c>
+      <c r="D20" t="n">
+        <v>66.73209028459274</v>
+      </c>
+      <c r="E20" t="n">
+        <v>66.36982447342565</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>52.1099116781158</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2.515919957309961</v>
+      </c>
+      <c r="D21" t="n">
+        <v>52.10991167811579</v>
+      </c>
+      <c r="E21" t="n">
+        <v>48.17078613963125</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>74.48478900883219</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5837389752268791</v>
+      </c>
+      <c r="D22" t="n">
+        <v>74.48478900883218</v>
+      </c>
+      <c r="E22" t="n">
+        <v>74.86315830789923</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>57.60549558390579</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.788294887170196</v>
+      </c>
+      <c r="D23" t="n">
+        <v>57.60549558390579</v>
+      </c>
+      <c r="E23" t="n">
+        <v>49.4456080288993</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>84.20019627085378</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.3719590846449137</v>
+      </c>
+      <c r="D24" t="n">
+        <v>84.20019627085378</v>
+      </c>
+      <c r="E24" t="n">
+        <v>84.23900100457354</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>61.62904808635918</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.140049016103148</v>
+      </c>
+      <c r="D25" t="n">
+        <v>61.62904808635917</v>
+      </c>
+      <c r="E25" t="n">
+        <v>60.4216818100331</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>63.98429833169774</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.351998647674918</v>
+      </c>
+      <c r="D26" t="n">
+        <v>63.98429833169774</v>
+      </c>
+      <c r="E26" t="n">
+        <v>63.7701168843406</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>55.74092247301276</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.246808582916856</v>
+      </c>
+      <c r="D27" t="n">
+        <v>55.74092247301275</v>
+      </c>
+      <c r="E27" t="n">
+        <v>55.06834964282219</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>56.82041216879293</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.012131549417973</v>
+      </c>
+      <c r="D28" t="n">
+        <v>56.82041216879293</v>
+      </c>
+      <c r="E28" t="n">
+        <v>55.22352661934068</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>92.24730127576055</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.2029216414084658</v>
+      </c>
+      <c r="D29" t="n">
+        <v>92.24730127576055</v>
+      </c>
+      <c r="E29" t="n">
+        <v>92.2741130774007</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>79.29342492639843</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.61482921642164</v>
+      </c>
+      <c r="D30" t="n">
+        <v>79.29342492639843</v>
+      </c>
+      <c r="E30" t="n">
+        <v>78.79498950509229</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>93.52306182531893</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.1764685181697132</v>
+      </c>
+      <c r="D31" t="n">
+        <v>93.52306182531895</v>
+      </c>
+      <c r="E31" t="n">
+        <v>93.53786334155998</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>66.90873405299314</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.08409718040372</v>
+      </c>
+      <c r="D32" t="n">
+        <v>66.90873405299314</v>
+      </c>
+      <c r="E32" t="n">
+        <v>65.27768132337744</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>12.98645796961677</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.575624355814974</v>
+      </c>
+      <c r="D33" t="n">
+        <v>12.98645796961677</v>
+      </c>
+      <c r="E33" t="n">
+        <v>14.50210073552758</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>54.56329735034348</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.663098567165434</v>
+      </c>
+      <c r="D2" t="n">
+        <v>54.56329735034348</v>
+      </c>
+      <c r="E2" t="n">
+        <v>47.63729403841872</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>38.27281648675172</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.444327809847891</v>
+      </c>
+      <c r="D3" t="n">
+        <v>38.27281648675172</v>
+      </c>
+      <c r="E3" t="n">
+        <v>32.2807994647812</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>79.78410206084396</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5427344292402267</v>
+      </c>
+      <c r="D4" t="n">
+        <v>79.78410206084396</v>
+      </c>
+      <c r="E4" t="n">
+        <v>79.3488953908942</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>49.75466143277723</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.494060784578323</v>
+      </c>
+      <c r="D5" t="n">
+        <v>49.75466143277723</v>
+      </c>
+      <c r="E5" t="n">
+        <v>48.53760556385854</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>69.18547595682041</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7108976542949677</v>
+      </c>
+      <c r="D6" t="n">
+        <v>69.18547595682041</v>
+      </c>
+      <c r="E6" t="n">
+        <v>69.17251225229013</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>45.53483807654563</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.339587330818176</v>
+      </c>
+      <c r="D7" t="n">
+        <v>45.53483807654563</v>
+      </c>
+      <c r="E7" t="n">
+        <v>45.05787161057033</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>60.15701668302257</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.292287190328352</v>
+      </c>
+      <c r="D8" t="n">
+        <v>60.15701668302257</v>
+      </c>
+      <c r="E8" t="n">
+        <v>57.97543932134477</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>67.02649656526006</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9356389356544241</v>
+      </c>
+      <c r="D9" t="n">
+        <v>67.02649656526006</v>
+      </c>
+      <c r="E9" t="n">
+        <v>65.22845163818293</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>81.648675171737</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.4428457506000996</v>
+      </c>
+      <c r="D10" t="n">
+        <v>81.648675171737</v>
+      </c>
+      <c r="E10" t="n">
+        <v>81.47868983341053</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>70.16683022571148</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8124630823731422</v>
+      </c>
+      <c r="D11" t="n">
+        <v>70.16683022571148</v>
+      </c>
+      <c r="E11" t="n">
+        <v>69.9811492504173</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>72.03140333660451</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.023755434667692</v>
+      </c>
+      <c r="D12" t="n">
+        <v>72.03140333660451</v>
+      </c>
+      <c r="E12" t="n">
+        <v>69.928642352903</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>66.92836113837095</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.032516784965992</v>
+      </c>
+      <c r="D13" t="n">
+        <v>66.92836113837095</v>
+      </c>
+      <c r="E13" t="n">
+        <v>66.87300483405575</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>58.88125613346418</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.167374891228974</v>
+      </c>
+      <c r="D14" t="n">
+        <v>58.88125613346418</v>
+      </c>
+      <c r="E14" t="n">
+        <v>53.17777723625674</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>56.13346418056918</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.332773433998227</v>
+      </c>
+      <c r="D15" t="n">
+        <v>56.13346418056918</v>
+      </c>
+      <c r="E15" t="n">
+        <v>51.55309877032981</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>53.18940137389598</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.607973489910364</v>
+      </c>
+      <c r="D16" t="n">
+        <v>53.18940137389598</v>
+      </c>
+      <c r="E16" t="n">
+        <v>46.71041529903802</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>68.59666339548578</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8988271728157997</v>
+      </c>
+      <c r="D17" t="n">
+        <v>68.59666339548576</v>
+      </c>
+      <c r="E17" t="n">
+        <v>68.83860681554876</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>56.23159960745829</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.307937823235989</v>
+      </c>
+      <c r="D18" t="n">
+        <v>56.23159960745829</v>
+      </c>
+      <c r="E18" t="n">
+        <v>58.59186014919364</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>82.23748773307165</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6254745393525809</v>
+      </c>
+      <c r="D19" t="n">
+        <v>82.23748773307163</v>
+      </c>
+      <c r="E19" t="n">
+        <v>81.85539554502196</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>59.66633954857704</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.505849789828062</v>
+      </c>
+      <c r="D20" t="n">
+        <v>59.66633954857704</v>
+      </c>
+      <c r="E20" t="n">
+        <v>59.45556199979033</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>57.89990186457311</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.778543725609779</v>
+      </c>
+      <c r="D21" t="n">
+        <v>57.89990186457311</v>
+      </c>
+      <c r="E21" t="n">
+        <v>56.58407594695824</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>67.81157998037291</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.8586109802126884</v>
+      </c>
+      <c r="D22" t="n">
+        <v>67.81157998037291</v>
+      </c>
+      <c r="E22" t="n">
+        <v>68.12680102704017</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>58.78312070657508</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.363261923193932</v>
+      </c>
+      <c r="D23" t="n">
+        <v>58.78312070657508</v>
+      </c>
+      <c r="E23" t="n">
+        <v>54.5286640836194</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>81.05986261040236</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.4492081981152296</v>
+      </c>
+      <c r="D24" t="n">
+        <v>81.05986261040236</v>
+      </c>
+      <c r="E24" t="n">
+        <v>81.1380478598539</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>52.79685966633955</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.634485252201557</v>
+      </c>
+      <c r="D25" t="n">
+        <v>52.79685966633954</v>
+      </c>
+      <c r="E25" t="n">
+        <v>52.6485819968018</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>68.40039254170756</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8966840282082558</v>
+      </c>
+      <c r="D26" t="n">
+        <v>68.40039254170756</v>
+      </c>
+      <c r="E26" t="n">
+        <v>68.87328825352685</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>61.13837095191364</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.005027696490288</v>
+      </c>
+      <c r="D27" t="n">
+        <v>61.13837095191364</v>
+      </c>
+      <c r="E27" t="n">
+        <v>61.13185993939637</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>55.93719332679097</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.042188182473183</v>
+      </c>
+      <c r="D28" t="n">
+        <v>55.93719332679097</v>
+      </c>
+      <c r="E28" t="n">
+        <v>55.92250169684293</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>83.61138370951913</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.6350572123192251</v>
+      </c>
+      <c r="D29" t="n">
+        <v>83.61138370951913</v>
+      </c>
+      <c r="E29" t="n">
+        <v>83.42138897238274</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>77.03631010794896</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6862254474617657</v>
+      </c>
+      <c r="D30" t="n">
+        <v>77.03631010794896</v>
+      </c>
+      <c r="E30" t="n">
+        <v>76.07366542148982</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>84.78900883218841</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.41700011305511</v>
+      </c>
+      <c r="D31" t="n">
+        <v>84.78900883218841</v>
+      </c>
+      <c r="E31" t="n">
+        <v>84.77218481831814</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>64.64180569185477</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.131557255141524</v>
+      </c>
+      <c r="D32" t="n">
+        <v>64.64180569185477</v>
+      </c>
+      <c r="E32" t="n">
+        <v>63.23013771275125</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>11.85696768045659</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.5785534216558594</v>
+      </c>
+      <c r="D33" t="n">
+        <v>11.85696768045659</v>
+      </c>
+      <c r="E33" t="n">
+        <v>13.08670567442233</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>49.55839057899902</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.175508970394731</v>
+      </c>
+      <c r="D2" t="n">
+        <v>49.55839057899902</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.24819791444698</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>37.68400392541707</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.070075616240501</v>
+      </c>
+      <c r="D3" t="n">
+        <v>37.68400392541707</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35.24264781474141</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>73.89597644749755</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.659247849136591</v>
+      </c>
+      <c r="D4" t="n">
+        <v>73.89597644749755</v>
+      </c>
+      <c r="E4" t="n">
+        <v>73.92572806078877</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>48.47890088321884</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.661856666207314</v>
+      </c>
+      <c r="D5" t="n">
+        <v>48.47890088321884</v>
+      </c>
+      <c r="E5" t="n">
+        <v>38.64170981769087</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>60.549558390579</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9820869341492653</v>
+      </c>
+      <c r="D6" t="n">
+        <v>60.54955839057899</v>
+      </c>
+      <c r="E6" t="n">
+        <v>60.38069718443627</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>39.450441609421</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.608706721104681</v>
+      </c>
+      <c r="D7" t="n">
+        <v>39.450441609421</v>
+      </c>
+      <c r="E7" t="n">
+        <v>27.67791338431854</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>62.90480863591757</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.324160976189887</v>
+      </c>
+      <c r="D8" t="n">
+        <v>62.90480863591756</v>
+      </c>
+      <c r="E8" t="n">
+        <v>61.8526531117343</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>66.83022571148184</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8862303330097347</v>
+      </c>
+      <c r="D9" t="n">
+        <v>66.83022571148184</v>
+      </c>
+      <c r="E9" t="n">
+        <v>66.14271628680528</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>75.9568204121688</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.5388545580208302</v>
+      </c>
+      <c r="D10" t="n">
+        <v>75.9568204121688</v>
+      </c>
+      <c r="E10" t="n">
+        <v>75.27908229900274</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>64.18056918547596</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9460900872945786</v>
+      </c>
+      <c r="D11" t="n">
+        <v>64.18056918547596</v>
+      </c>
+      <c r="E11" t="n">
+        <v>63.89375707971202</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>69.47988223748773</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9015925694257021</v>
+      </c>
+      <c r="D12" t="n">
+        <v>69.47988223748773</v>
+      </c>
+      <c r="E12" t="n">
+        <v>67.97157564825574</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>61.82531894013739</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.314387075603008</v>
+      </c>
+      <c r="D13" t="n">
+        <v>61.82531894013739</v>
+      </c>
+      <c r="E13" t="n">
+        <v>60.22084121875151</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>61.43277723258096</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9774741772562265</v>
+      </c>
+      <c r="D14" t="n">
+        <v>61.43277723258096</v>
+      </c>
+      <c r="E14" t="n">
+        <v>59.55704985368841</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>54.85770363101079</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.300379861146212</v>
+      </c>
+      <c r="D15" t="n">
+        <v>54.85770363101079</v>
+      </c>
+      <c r="E15" t="n">
+        <v>52.43353414047031</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>53.4838076545633</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.420240201056004</v>
+      </c>
+      <c r="D16" t="n">
+        <v>53.4838076545633</v>
+      </c>
+      <c r="E16" t="n">
+        <v>53.21010004638278</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>58.09617271835133</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.571554617956281</v>
+      </c>
+      <c r="D17" t="n">
+        <v>58.09617271835133</v>
+      </c>
+      <c r="E17" t="n">
+        <v>58.39505135729763</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>55.15210991167812</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.169718511402607</v>
+      </c>
+      <c r="D18" t="n">
+        <v>55.15210991167812</v>
+      </c>
+      <c r="E18" t="n">
+        <v>54.75157877729681</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>65.06378802747793</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.134446337819099</v>
+      </c>
+      <c r="D19" t="n">
+        <v>65.06378802747793</v>
+      </c>
+      <c r="E19" t="n">
+        <v>61.51531718869352</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>54.66143277723258</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.770185794681311</v>
+      </c>
+      <c r="D20" t="n">
+        <v>54.66143277723258</v>
+      </c>
+      <c r="E20" t="n">
+        <v>53.27000121708689</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>60.25515210991168</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.584668694064021</v>
+      </c>
+      <c r="D21" t="n">
+        <v>60.25515210991168</v>
+      </c>
+      <c r="E21" t="n">
+        <v>60.3975855462126</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>52.99313052011776</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.218541296198964</v>
+      </c>
+      <c r="D22" t="n">
+        <v>52.99313052011776</v>
+      </c>
+      <c r="E22" t="n">
+        <v>43.33624266763724</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>62.80667320902846</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.951032217592001</v>
+      </c>
+      <c r="D23" t="n">
+        <v>62.80667320902846</v>
+      </c>
+      <c r="E23" t="n">
+        <v>63.01407505533048</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>68.40039254170756</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.7377243861556053</v>
+      </c>
+      <c r="D24" t="n">
+        <v>68.40039254170756</v>
+      </c>
+      <c r="E24" t="n">
+        <v>68.03642867500103</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>46.90873405299313</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.48708762601018</v>
+      </c>
+      <c r="D25" t="n">
+        <v>46.90873405299313</v>
+      </c>
+      <c r="E25" t="n">
+        <v>46.86392781014905</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>53.77821393523062</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.419796407222748</v>
+      </c>
+      <c r="D26" t="n">
+        <v>53.77821393523062</v>
+      </c>
+      <c r="E26" t="n">
+        <v>53.72298341472261</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>44.35721295387635</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.581166060641408</v>
+      </c>
+      <c r="D27" t="n">
+        <v>44.35721295387635</v>
+      </c>
+      <c r="E27" t="n">
+        <v>44.0231538008899</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>62.11972522080471</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9332141578197479</v>
+      </c>
+      <c r="D28" t="n">
+        <v>62.11972522080471</v>
+      </c>
+      <c r="E28" t="n">
+        <v>60.36323419536708</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>66.83022571148184</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.368424942716956</v>
+      </c>
+      <c r="D29" t="n">
+        <v>66.83022571148184</v>
+      </c>
+      <c r="E29" t="n">
+        <v>63.44449765073185</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>63.19921491658489</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.089953020666144</v>
+      </c>
+      <c r="D30" t="n">
+        <v>63.19921491658489</v>
+      </c>
+      <c r="E30" t="n">
+        <v>58.59690336249835</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>82.92443572129538</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.5356416826252826</v>
+      </c>
+      <c r="D31" t="n">
+        <v>82.92443572129538</v>
+      </c>
+      <c r="E31" t="n">
+        <v>82.77533558946921</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>59.27052666012431</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.377334944993587</v>
+      </c>
+      <c r="D32" t="n">
+        <v>59.27052666012431</v>
+      </c>
+      <c r="E32" t="n">
+        <v>57.07281733898701</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>10.13476513539604</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6110480809363563</v>
+      </c>
+      <c r="D33" t="n">
+        <v>10.13476513539604</v>
+      </c>
+      <c r="E33" t="n">
+        <v>11.85678543358483</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>45.53483807654563</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.146112317219377</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.53483807654563</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.383257697445</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>37.48773307163886</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.443519204854965</v>
+      </c>
+      <c r="D3" t="n">
+        <v>37.48773307163886</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35.97999140821702</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>56.52600588812561</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9892377816140652</v>
+      </c>
+      <c r="D4" t="n">
+        <v>56.52600588812562</v>
+      </c>
+      <c r="E4" t="n">
+        <v>55.05371100078021</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>39.05789990186457</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.563688270747662</v>
+      </c>
+      <c r="D5" t="n">
+        <v>39.05789990186458</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30.88513239766768</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>46.12365063788027</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.194355167448521</v>
+      </c>
+      <c r="D6" t="n">
+        <v>46.12365063788027</v>
+      </c>
+      <c r="E6" t="n">
+        <v>41.59850138884658</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>32.48282630029441</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.665119975805283</v>
+      </c>
+      <c r="D7" t="n">
+        <v>32.48282630029441</v>
+      </c>
+      <c r="E7" t="n">
+        <v>28.30804500266118</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>61.13837095191364</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.719472006618162</v>
+      </c>
+      <c r="D8" t="n">
+        <v>61.13837095191364</v>
+      </c>
+      <c r="E8" t="n">
+        <v>58.88770037706816</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>64.37684003925418</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9522744313580915</v>
+      </c>
+      <c r="D9" t="n">
+        <v>64.37684003925416</v>
+      </c>
+      <c r="E9" t="n">
+        <v>63.22536613994509</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>79.09715407262021</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.5528619270771742</v>
+      </c>
+      <c r="D10" t="n">
+        <v>79.09715407262021</v>
+      </c>
+      <c r="E10" t="n">
+        <v>78.61031908187938</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>62.0215897939156</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.27423369884491</v>
+      </c>
+      <c r="D11" t="n">
+        <v>62.0215897939156</v>
+      </c>
+      <c r="E11" t="n">
+        <v>61.36685217540957</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>70.3631010794897</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9008956290781498</v>
+      </c>
+      <c r="D12" t="n">
+        <v>70.3631010794897</v>
+      </c>
+      <c r="E12" t="n">
+        <v>68.73300853456216</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>50.24533856722277</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.60410107858479</v>
+      </c>
+      <c r="D13" t="n">
+        <v>50.24533856722277</v>
+      </c>
+      <c r="E13" t="n">
+        <v>52.01646490495586</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>62.21786064769382</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.107366455253214</v>
+      </c>
+      <c r="D14" t="n">
+        <v>62.21786064769381</v>
+      </c>
+      <c r="E14" t="n">
+        <v>59.16600356802688</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>32.77723258096173</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.115635469555855</v>
+      </c>
+      <c r="D15" t="n">
+        <v>32.77723258096173</v>
+      </c>
+      <c r="E15" t="n">
+        <v>29.55347744263759</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>58.39057899901864</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.062860296107829</v>
+      </c>
+      <c r="D16" t="n">
+        <v>58.39057899901865</v>
+      </c>
+      <c r="E16" t="n">
+        <v>56.276655013153</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>57.60549558390579</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.382824685424566</v>
+      </c>
+      <c r="D17" t="n">
+        <v>57.60549558390579</v>
+      </c>
+      <c r="E17" t="n">
+        <v>57.95504574603726</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>47.98822374877331</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.266583167016506</v>
+      </c>
+      <c r="D18" t="n">
+        <v>47.98822374877331</v>
+      </c>
+      <c r="E18" t="n">
+        <v>51.16580040035777</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>64.27870461236506</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.021376702934504</v>
+      </c>
+      <c r="D19" t="n">
+        <v>64.27870461236506</v>
+      </c>
+      <c r="E19" t="n">
+        <v>63.90590499017411</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>52.99313052011776</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.974452149122953</v>
+      </c>
+      <c r="D20" t="n">
+        <v>52.99313052011776</v>
+      </c>
+      <c r="E20" t="n">
+        <v>49.5621939664807</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>58.09617271835133</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.718600749969482</v>
+      </c>
+      <c r="D21" t="n">
+        <v>58.09617271835133</v>
+      </c>
+      <c r="E21" t="n">
+        <v>57.91913075308109</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>53.97448478900883</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.331000715494156</v>
+      </c>
+      <c r="D22" t="n">
+        <v>53.97448478900883</v>
+      </c>
+      <c r="E22" t="n">
+        <v>48.3152541735481</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>39.74484789008832</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.054435059428215</v>
+      </c>
+      <c r="D23" t="n">
+        <v>39.74484789008832</v>
+      </c>
+      <c r="E23" t="n">
+        <v>30.82139570763414</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>56.72227674190383</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9686139859259129</v>
+      </c>
+      <c r="D24" t="n">
+        <v>56.72227674190383</v>
+      </c>
+      <c r="E24" t="n">
+        <v>56.40883955145196</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>36.01570166830226</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.034539796411991</v>
+      </c>
+      <c r="D25" t="n">
+        <v>36.01570166830226</v>
+      </c>
+      <c r="E25" t="n">
+        <v>31.11773528846269</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>51.71736997055937</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.281551398336887</v>
+      </c>
+      <c r="D26" t="n">
+        <v>51.71736997055937</v>
+      </c>
+      <c r="E26" t="n">
+        <v>52.45080146085469</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>41.21687929342492</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.711693353950977</v>
+      </c>
+      <c r="D27" t="n">
+        <v>41.21687929342492</v>
+      </c>
+      <c r="E27" t="n">
+        <v>36.29501677630224</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>60.35328753680079</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8933573216199875</v>
+      </c>
+      <c r="D28" t="n">
+        <v>60.35328753680078</v>
+      </c>
+      <c r="E28" t="n">
+        <v>58.49822184560765</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>68.40039254170756</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8311191610991955</v>
+      </c>
+      <c r="D29" t="n">
+        <v>68.40039254170756</v>
+      </c>
+      <c r="E29" t="n">
+        <v>68.04572347707784</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>60.25515210991168</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.348727839736966</v>
+      </c>
+      <c r="D30" t="n">
+        <v>60.25515210991168</v>
+      </c>
+      <c r="E30" t="n">
+        <v>54.73455826688169</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>84.98527968596663</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.4926329490845092</v>
+      </c>
+      <c r="D31" t="n">
+        <v>84.98527968596663</v>
+      </c>
+      <c r="E31" t="n">
+        <v>84.88640186640393</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>54.40628066732089</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.453441424857495</v>
+      </c>
+      <c r="D32" t="n">
+        <v>54.40628066732089</v>
+      </c>
+      <c r="E32" t="n">
+        <v>51.93755034678705</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>12.76473970775361</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.5822216628206047</v>
+      </c>
+      <c r="D33" t="n">
+        <v>12.76473970775361</v>
+      </c>
+      <c r="E33" t="n">
+        <v>14.39894380098364</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>38.66535819430815</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.759174589067698</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.66535819430815</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.7237903949406</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>40.23552502453386</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.421656250953674</v>
+      </c>
+      <c r="D3" t="n">
+        <v>40.23552502453386</v>
+      </c>
+      <c r="E3" t="n">
+        <v>37.34209953991905</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>59.56820412168793</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9675925895571709</v>
+      </c>
+      <c r="D4" t="n">
+        <v>59.56820412168793</v>
+      </c>
+      <c r="E4" t="n">
+        <v>59.26657557117972</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>37.48773307163886</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.229593381285667</v>
+      </c>
+      <c r="D5" t="n">
+        <v>37.48773307163886</v>
+      </c>
+      <c r="E5" t="n">
+        <v>34.89386388804425</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>35.42688910696761</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.246428862214088</v>
+      </c>
+      <c r="D6" t="n">
+        <v>35.42688910696761</v>
+      </c>
+      <c r="E6" t="n">
+        <v>32.91119838890344</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>28.36113837095191</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.563883155584335</v>
+      </c>
+      <c r="D7" t="n">
+        <v>28.36113837095192</v>
+      </c>
+      <c r="E7" t="n">
+        <v>21.57013050940285</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>62.90480863591757</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9303823680675123</v>
+      </c>
+      <c r="D8" t="n">
+        <v>62.90480863591756</v>
+      </c>
+      <c r="E8" t="n">
+        <v>61.79248384542827</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>63.88616290480864</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.7574017979204655</v>
+      </c>
+      <c r="D9" t="n">
+        <v>63.88616290480864</v>
+      </c>
+      <c r="E9" t="n">
+        <v>62.94833374223096</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>66.14327772325809</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.828437365591526</v>
+      </c>
+      <c r="D10" t="n">
+        <v>66.14327772325809</v>
+      </c>
+      <c r="E10" t="n">
+        <v>63.4954582646405</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>56.3297350343474</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.060451664030552</v>
+      </c>
+      <c r="D11" t="n">
+        <v>56.32973503434739</v>
+      </c>
+      <c r="E11" t="n">
+        <v>58.25380737675371</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>54.56329735034348</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.02111804485321</v>
+      </c>
+      <c r="D12" t="n">
+        <v>54.56329735034348</v>
+      </c>
+      <c r="E12" t="n">
+        <v>54.13888801908969</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>40.62806673209028</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.354787925258279</v>
+      </c>
+      <c r="D13" t="n">
+        <v>40.62806673209028</v>
+      </c>
+      <c r="E13" t="n">
+        <v>38.70812139694942</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>46.90873405299313</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.650814582593739</v>
+      </c>
+      <c r="D14" t="n">
+        <v>46.90873405299313</v>
+      </c>
+      <c r="E14" t="n">
+        <v>38.61523818174195</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>31.0107948969578</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.25230648368597</v>
+      </c>
+      <c r="D15" t="n">
+        <v>31.0107948969578</v>
+      </c>
+      <c r="E15" t="n">
+        <v>29.30745945245117</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>49.06771344455348</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.022259425371885</v>
+      </c>
+      <c r="D16" t="n">
+        <v>49.06771344455348</v>
+      </c>
+      <c r="E16" t="n">
+        <v>48.52275772467846</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>42.59077526987242</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.798280321061611</v>
+      </c>
+      <c r="D17" t="n">
+        <v>42.59077526987242</v>
+      </c>
+      <c r="E17" t="n">
+        <v>41.12241983829206</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>55.05397448478901</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.92630784958601</v>
+      </c>
+      <c r="D18" t="n">
+        <v>55.053974484789</v>
+      </c>
+      <c r="E18" t="n">
+        <v>56.44636769047213</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>44.06280667320903</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.331264279782772</v>
+      </c>
+      <c r="D19" t="n">
+        <v>44.06280667320902</v>
+      </c>
+      <c r="E19" t="n">
+        <v>44.03076538985292</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>43.27772325809617</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.435653619468212</v>
+      </c>
+      <c r="D20" t="n">
+        <v>43.27772325809617</v>
+      </c>
+      <c r="E20" t="n">
+        <v>38.76524832234605</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>58.29244357212954</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.247641112655401</v>
+      </c>
+      <c r="D21" t="n">
+        <v>58.29244357212954</v>
+      </c>
+      <c r="E21" t="n">
+        <v>58.15846699085839</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>49.16584887144259</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.047850087285042</v>
+      </c>
+      <c r="D22" t="n">
+        <v>49.16584887144259</v>
+      </c>
+      <c r="E22" t="n">
+        <v>40.45759473418269</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>38.37095191364082</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.671086184680462</v>
+      </c>
+      <c r="D23" t="n">
+        <v>38.37095191364082</v>
+      </c>
+      <c r="E23" t="n">
+        <v>28.36465216842566</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>49.36211972522081</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9756841361522675</v>
+      </c>
+      <c r="D24" t="n">
+        <v>49.36211972522081</v>
+      </c>
+      <c r="E24" t="n">
+        <v>48.05827155612664</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>40.13738959764475</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.973446752876043</v>
+      </c>
+      <c r="D25" t="n">
+        <v>40.13738959764475</v>
+      </c>
+      <c r="E25" t="n">
+        <v>38.15360100402347</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>54.66143277723258</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.118774227797985</v>
+      </c>
+      <c r="D26" t="n">
+        <v>54.66143277723258</v>
+      </c>
+      <c r="E26" t="n">
+        <v>55.21638500738855</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>37.78213935230618</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.311840277165174</v>
+      </c>
+      <c r="D27" t="n">
+        <v>37.78213935230618</v>
+      </c>
+      <c r="E27" t="n">
+        <v>36.11020113635431</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>39.25417075564279</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.340478552505374</v>
+      </c>
+      <c r="D28" t="n">
+        <v>39.25417075564279</v>
+      </c>
+      <c r="E28" t="n">
+        <v>35.06499094415168</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>68.89106967615309</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8370342329144478</v>
+      </c>
+      <c r="D29" t="n">
+        <v>68.89106967615309</v>
+      </c>
+      <c r="E29" t="n">
+        <v>68.59539417634159</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>66.63395485770363</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.00621611639508</v>
+      </c>
+      <c r="D30" t="n">
+        <v>66.63395485770363</v>
+      </c>
+      <c r="E30" t="n">
+        <v>65.57862795725124</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>77.82139352306183</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7651364868506789</v>
+      </c>
+      <c r="D31" t="n">
+        <v>77.82139352306181</v>
+      </c>
+      <c r="E31" t="n">
+        <v>77.61523856863285</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>49.21818776578345</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.261766090773744</v>
+      </c>
+      <c r="D32" t="n">
+        <v>49.21818776578345</v>
+      </c>
+      <c r="E32" t="n">
+        <v>46.74094772603515</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>12.15350198802922</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.3488496420385789</v>
+      </c>
+      <c r="D33" t="n">
+        <v>12.15350198802922</v>
+      </c>
+      <c r="E33" t="n">
+        <v>13.92420191836523</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>40.8243375858685</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.973464120179415</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.8243375858685</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.56100864298299</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>40.92247301275761</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.225997008383274</v>
+      </c>
+      <c r="D3" t="n">
+        <v>40.92247301275761</v>
+      </c>
+      <c r="E3" t="n">
+        <v>38.68333745217976</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>29.44062806673209</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.206714328378439</v>
+      </c>
+      <c r="D4" t="n">
+        <v>29.44062806673209</v>
+      </c>
+      <c r="E4" t="n">
+        <v>24.63966769243034</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>24.92639842983317</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.54726967215538</v>
+      </c>
+      <c r="D5" t="n">
+        <v>24.92639842983317</v>
+      </c>
+      <c r="E5" t="n">
+        <v>15.58831554110439</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>32.97350343473994</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.174327075481415</v>
+      </c>
+      <c r="D6" t="n">
+        <v>32.97350343473994</v>
+      </c>
+      <c r="E6" t="n">
+        <v>32.43456610750049</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>31.30520117762512</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.692946158349514</v>
+      </c>
+      <c r="D7" t="n">
+        <v>31.30520117762513</v>
+      </c>
+      <c r="E7" t="n">
+        <v>23.98940504933013</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>63.78802747791953</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8320890649483772</v>
+      </c>
+      <c r="D8" t="n">
+        <v>63.78802747791953</v>
+      </c>
+      <c r="E8" t="n">
+        <v>62.73907563030412</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>55.15210991167812</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8304010480642319</v>
+      </c>
+      <c r="D9" t="n">
+        <v>55.15210991167812</v>
+      </c>
+      <c r="E9" t="n">
+        <v>55.24265799089142</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>60.64769381746811</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.8020410910248756</v>
+      </c>
+      <c r="D10" t="n">
+        <v>60.64769381746811</v>
+      </c>
+      <c r="E10" t="n">
+        <v>60.3222928533125</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>42.198233562316</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.251413628458977</v>
+      </c>
+      <c r="D11" t="n">
+        <v>42.198233562316</v>
+      </c>
+      <c r="E11" t="n">
+        <v>42.93343266342945</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>43.17958783120707</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.091500766575336</v>
+      </c>
+      <c r="D12" t="n">
+        <v>43.17958783120707</v>
+      </c>
+      <c r="E12" t="n">
+        <v>42.1518395814321</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>43.76840039254171</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.224781781435013</v>
+      </c>
+      <c r="D13" t="n">
+        <v>43.76840039254171</v>
+      </c>
+      <c r="E13" t="n">
+        <v>44.38440464507688</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>50.34347399411187</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.877726927399635</v>
+      </c>
+      <c r="D14" t="n">
+        <v>50.34347399411187</v>
+      </c>
+      <c r="E14" t="n">
+        <v>42.38444657921239</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>37.48773307163886</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.598676592111588</v>
+      </c>
+      <c r="D15" t="n">
+        <v>37.48773307163886</v>
+      </c>
+      <c r="E15" t="n">
+        <v>27.9804018170244</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>35.2306182531894</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.386253833770752</v>
+      </c>
+      <c r="D16" t="n">
+        <v>35.2306182531894</v>
+      </c>
+      <c r="E16" t="n">
+        <v>28.3749521096522</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>46.90873405299313</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.142797514796257</v>
+      </c>
+      <c r="D17" t="n">
+        <v>46.90873405299313</v>
+      </c>
+      <c r="E17" t="n">
+        <v>45.55379097979977</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>42.98331697742885</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.179037109017372</v>
+      </c>
+      <c r="D18" t="n">
+        <v>42.98331697742886</v>
+      </c>
+      <c r="E18" t="n">
+        <v>44.61633194769521</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>47.98822374877331</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.158470697700977</v>
+      </c>
+      <c r="D19" t="n">
+        <v>47.98822374877331</v>
+      </c>
+      <c r="E19" t="n">
+        <v>48.50659917007359</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>42.88518155053975</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.545614749193192</v>
+      </c>
+      <c r="D20" t="n">
+        <v>42.88518155053975</v>
+      </c>
+      <c r="E20" t="n">
+        <v>32.28843838802744</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>47.59568204121688</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.40689205378294</v>
+      </c>
+      <c r="D21" t="n">
+        <v>47.59568204121688</v>
+      </c>
+      <c r="E21" t="n">
+        <v>47.75891409944131</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>54.66143277723258</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.9910485483705997</v>
+      </c>
+      <c r="D22" t="n">
+        <v>54.66143277723258</v>
+      </c>
+      <c r="E22" t="n">
+        <v>53.16407463175915</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>33.56231599607458</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.250705450773239</v>
+      </c>
+      <c r="D23" t="n">
+        <v>33.56231599607458</v>
+      </c>
+      <c r="E23" t="n">
+        <v>32.52294743460203</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>36.40824337585868</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.18505997210741</v>
+      </c>
+      <c r="D24" t="n">
+        <v>36.40824337585868</v>
+      </c>
+      <c r="E24" t="n">
+        <v>34.38981946536776</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>38.07654563297351</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.81719321757555</v>
+      </c>
+      <c r="D25" t="n">
+        <v>38.0765456329735</v>
+      </c>
+      <c r="E25" t="n">
+        <v>35.85784090872167</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>42.10009813542689</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.242370933294296</v>
+      </c>
+      <c r="D26" t="n">
+        <v>42.10009813542689</v>
+      </c>
+      <c r="E26" t="n">
+        <v>42.17225500869694</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>41.11874386653582</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.38660217449069</v>
+      </c>
+      <c r="D27" t="n">
+        <v>41.11874386653582</v>
+      </c>
+      <c r="E27" t="n">
+        <v>35.74538803759397</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>23.45436702649657</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.613867454230785</v>
+      </c>
+      <c r="D28" t="n">
+        <v>23.45436702649656</v>
+      </c>
+      <c r="E28" t="n">
+        <v>18.19904114369964</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>61.53091265947007</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.9149838015437126</v>
+      </c>
+      <c r="D29" t="n">
+        <v>61.53091265947007</v>
+      </c>
+      <c r="E29" t="n">
+        <v>61.38756061661886</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>67.12463199214916</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8972946674621198</v>
+      </c>
+      <c r="D30" t="n">
+        <v>67.12463199214916</v>
+      </c>
+      <c r="E30" t="n">
+        <v>66.07828605425831</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>55.54465161923454</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.428868488408625</v>
+      </c>
+      <c r="D31" t="n">
+        <v>55.54465161923454</v>
+      </c>
+      <c r="E31" t="n">
+        <v>56.03955310523296</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>43.80438338240105</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.329213664315466</v>
+      </c>
+      <c r="D32" t="n">
+        <v>43.80438338240106</v>
+      </c>
+      <c r="E32" t="n">
+        <v>40.95635484491507</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>10.95115395403811</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.3465204410217747</v>
+      </c>
+      <c r="D33" t="n">
+        <v>10.95115395403811</v>
+      </c>
+      <c r="E33" t="n">
+        <v>13.00016207373773</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>